--- a/Excel/ParaHacerRowing11Jul2023.xlsx
+++ b/Excel/ParaHacerRowing11Jul2023.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Flutter\rowing_app\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8551583-5E6B-4235-83DE-8BC92FF749E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE844410-9983-4CA0-B746-A0E3D284B024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>FROM     Obras</t>
   </si>
@@ -63,7 +63,16 @@
     <t>Planos</t>
   </si>
   <si>
-    <t>SELECT NroObra, POSX, POSY, Direccion,TextoLocalizacion, TextoClase, TextoTipo, TextoComponente, CodigoDiametro, Motivo, Planos</t>
+    <t>SELECT IdUsuario, Nombre, Apellido, Login, Contrasena, RUBRO, CONCEPTOMOVA, LimitarGrupo, HabilitaAPP, HabilitaFotos</t>
+  </si>
+  <si>
+    <t>FROM     Usuarios</t>
+  </si>
+  <si>
+    <t>WHERE  (Modulo = 'Aysa')</t>
+  </si>
+  <si>
+    <t>SELECT NroObra, POSX, POSY, Direccion, TextoLocalizacion, TextoClase, TextoTipo, TextoComponente, CodigoDiametro, Motivo, Planos</t>
   </si>
 </sst>
 </file>
@@ -381,28 +390,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>2</v>
       </c>
@@ -412,8 +426,11 @@
       <c r="D6">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>3</v>
       </c>
@@ -423,8 +440,11 @@
       <c r="D7">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>5</v>
       </c>
@@ -435,7 +455,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>6</v>
       </c>
@@ -446,7 +466,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>7</v>
       </c>
@@ -457,7 +477,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -468,7 +488,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>9</v>
       </c>
@@ -479,7 +499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -490,7 +510,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>11</v>
       </c>
